--- a/data/trans_camb/P19C01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,87</t>
+          <t>-6,05; 4,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 17,03</t>
+          <t>6,4; 17,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,55; 34,22</t>
+          <t>22,05; 34,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 11,63</t>
+          <t>0,92; 11,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 19,19</t>
+          <t>8,22; 19,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 31,16</t>
+          <t>21,52; 31,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 6,11</t>
+          <t>-1,18; 6,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,52</t>
+          <t>9,06; 16,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 30,92</t>
+          <t>22,98; 31,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 18,76</t>
+          <t>-23,55; 23,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,02; 81,89</t>
+          <t>24,49; 88,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,89; 173,29</t>
+          <t>84,06; 172,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 49,13</t>
+          <t>3,2; 48,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,54; 81,38</t>
+          <t>29,22; 85,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,76; 133,24</t>
+          <t>72,85; 135,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 26,76</t>
+          <t>-4,45; 27,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 73,8</t>
+          <t>33,35; 73,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,29; 138,19</t>
+          <t>85,4; 135,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,87</t>
+          <t>-5,32; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,34</t>
+          <t>5,7; 15,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 31,08</t>
+          <t>-4,11; 31,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 5,51</t>
+          <t>-4,24; 4,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,36</t>
+          <t>3,6; 13,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,36; 32,95</t>
+          <t>24,25; 32,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,45</t>
+          <t>-3,55; 3,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,74</t>
+          <t>6,16; 13,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 29,81</t>
+          <t>1,51; 29,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 13,58</t>
+          <t>-16,3; 15,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 56,46</t>
+          <t>17,17; 58,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 106,11</t>
+          <t>-12,54; 109,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 18,26</t>
+          <t>-12,08; 16,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,93; 44,22</t>
+          <t>10,27; 43,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,42; 110,33</t>
+          <t>68,82; 111,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 11,5</t>
+          <t>-10,66; 10,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,36; 42,7</t>
+          <t>18,41; 44,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 97,76</t>
+          <t>9,65; 97,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,95</t>
+          <t>-2,25; 8,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 17,18</t>
+          <t>4,53; 16,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,48; 32,53</t>
+          <t>20,11; 32,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 9,58</t>
+          <t>-0,18; 9,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 20,49</t>
+          <t>9,78; 20,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 26,06</t>
+          <t>-9,78; 26,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,07</t>
+          <t>0,16; 7,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 16,59</t>
+          <t>8,78; 16,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 26,59</t>
+          <t>-0,26; 26,69</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 35,02</t>
+          <t>-7,23; 33,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,58; 69,43</t>
+          <t>14,22; 63,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,52; 129,15</t>
+          <t>61,73; 122,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 37,76</t>
+          <t>-0,49; 39,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,67; 83,2</t>
+          <t>32,14; 82,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 95,93</t>
+          <t>-32,45; 97,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 30,53</t>
+          <t>0,65; 29,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,08; 62,44</t>
+          <t>29,52; 63,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 96,81</t>
+          <t>-0,53; 96,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 2,8</t>
+          <t>-7,35; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,89</t>
+          <t>5,82; 15,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,46; 32,49</t>
+          <t>21,82; 32,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,11</t>
+          <t>-2,95; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 16,6</t>
+          <t>7,14; 17,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,89; 36,78</t>
+          <t>25,41; 37,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,03</t>
+          <t>-3,75; 3,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,94; 14,9</t>
+          <t>7,71; 14,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,35; 33,56</t>
+          <t>25,58; 33,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 9,07</t>
+          <t>-19,62; 8,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,8; 48,34</t>
+          <t>15,56; 48,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,58; 102,53</t>
+          <t>57,4; 101,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 17,78</t>
+          <t>-7,69; 18,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,89; 49,19</t>
+          <t>18,61; 50,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,14; 105,62</t>
+          <t>65,17; 110,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 9,06</t>
+          <t>-9,97; 9,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,41; 44,34</t>
+          <t>20,86; 43,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67,31; 99,84</t>
+          <t>66,96; 98,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,03</t>
+          <t>-2,77; 2,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,67</t>
+          <t>8,22; 13,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,73; 28,69</t>
+          <t>11,13; 28,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,51</t>
+          <t>0,27; 5,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,7</t>
+          <t>9,48; 14,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,16; 29,07</t>
+          <t>12,99; 28,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,1</t>
+          <t>-0,47; 3,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,31</t>
+          <t>9,71; 13,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,89; 27,91</t>
+          <t>16,28; 27,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,14</t>
+          <t>-8,95; 8,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26,74; 47,87</t>
+          <t>26,39; 48,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38,95; 98,94</t>
+          <t>34,43; 97,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,0; 18,41</t>
+          <t>0,93; 17,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,64; 48,73</t>
+          <t>28,62; 48,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,6; 94,76</t>
+          <t>42,59; 93,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 10,51</t>
+          <t>-1,49; 10,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>29,96; 44,95</t>
+          <t>30,89; 44,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56,86; 92,73</t>
+          <t>53,66; 91,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,03</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,61</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,26</t>
+          <t>27,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 4,7</t>
+          <t>-6,51; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 17,41</t>
+          <t>6,38; 17,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,05; 34,11</t>
+          <t>21,45; 33,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 11,34</t>
+          <t>1,0; 11,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 19,32</t>
+          <t>7,99; 19,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 31,26</t>
+          <t>21,71; 31,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 6,11</t>
+          <t>-1,41; 6,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 16,74</t>
+          <t>7,99; 16,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 31,09</t>
+          <t>23,16; 30,31</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121,69%</t>
+          <t>118,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>101,24%</t>
+          <t>101,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>110,09%</t>
+          <t>109,05%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 23,16</t>
+          <t>-24,92; 22,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 88,14</t>
+          <t>23,94; 87,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,06; 172,61</t>
+          <t>80,01; 160,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 48,32</t>
+          <t>3,47; 51,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 85,0</t>
+          <t>27,29; 81,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,85; 135,41</t>
+          <t>72,87; 134,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 27,27</t>
+          <t>-5,22; 26,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,35; 73,34</t>
+          <t>30,16; 70,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,4; 135,9</t>
+          <t>85,84; 134,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,11</t>
+          <t>29,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,67</t>
+          <t>29,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22,06</t>
+          <t>29,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,34</t>
+          <t>-4,99; 4,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,85</t>
+          <t>5,54; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 31,1</t>
+          <t>24,81; 34,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,99</t>
+          <t>-3,8; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,05</t>
+          <t>3,81; 12,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,25; 32,98</t>
+          <t>24,85; 33,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,24</t>
+          <t>-3,15; 3,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,28</t>
+          <t>6,15; 13,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 29,99</t>
+          <t>25,85; 32,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 15,86</t>
+          <t>-15,66; 16,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 58,76</t>
+          <t>16,67; 58,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 109,38</t>
+          <t>74,62; 125,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 16,41</t>
+          <t>-10,77; 17,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 43,4</t>
+          <t>11,29; 43,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,82; 111,33</t>
+          <t>70,63; 111,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 10,72</t>
+          <t>-9,45; 11,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 44,47</t>
+          <t>18,2; 43,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 97,75</t>
+          <t>75,28; 109,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25,98</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,22 +1081,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>27,08</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,06</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>12,68</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12,68</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,31</t>
+          <t>26,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,75</t>
+          <t>-2,03; 9,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 16,34</t>
+          <t>4,25; 15,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,11; 32,36</t>
+          <t>19,78; 31,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,71</t>
+          <t>-0,7; 10,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 20,6</t>
+          <t>9,59; 20,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 26,53</t>
+          <t>21,99; 31,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 7,74</t>
+          <t>0,21; 7,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 16,87</t>
+          <t>8,25; 16,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 26,69</t>
+          <t>22,55; 30,28</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 33,82</t>
+          <t>-6,7; 35,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,22; 63,09</t>
+          <t>13,35; 60,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,73; 122,73</t>
+          <t>62,07; 121,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 39,08</t>
+          <t>-2,45; 42,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,14; 82,57</t>
+          <t>31,81; 81,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 97,87</t>
+          <t>71,64; 127,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 29,22</t>
+          <t>0,73; 29,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,52; 63,45</t>
+          <t>27,37; 63,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 96,0</t>
+          <t>74,81; 115,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27,19</t>
+          <t>26,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,96</t>
+          <t>27,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28,71</t>
+          <t>27,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 2,7</t>
+          <t>-7,66; 2,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,96</t>
+          <t>5,85; 16,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,82; 32,65</t>
+          <t>21,39; 31,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 6,32</t>
+          <t>-2,97; 6,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 17,04</t>
+          <t>6,94; 16,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,41; 37,73</t>
+          <t>23,21; 31,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,16</t>
+          <t>-3,8; 3,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,82</t>
+          <t>8,2; 14,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,58; 33,56</t>
+          <t>23,4; 30,03</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 8,4</t>
+          <t>-20,13; 8,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,56; 48,9</t>
+          <t>14,99; 50,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57,4; 101,71</t>
+          <t>56,95; 96,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,61; 50,36</t>
+          <t>18,13; 50,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,17; 110,87</t>
+          <t>59,81; 94,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 9,65</t>
+          <t>-10,12; 9,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,86; 43,67</t>
+          <t>21,58; 44,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66,96; 98,13</t>
+          <t>62,56; 89,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23,58</t>
+          <t>27,25</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,43</t>
+          <t>27,74</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24,0</t>
+          <t>27,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,36</t>
+          <t>-3,28; 1,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,7</t>
+          <t>8,47; 13,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,13; 28,62</t>
+          <t>24,49; 30,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,26</t>
+          <t>0,06; 5,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,79</t>
+          <t>9,36; 14,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,99; 28,78</t>
+          <t>25,5; 29,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,17</t>
+          <t>-0,64; 3,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,25</t>
+          <t>9,64; 13,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,45</t>
+          <t>25,5; 29,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 8,31</t>
+          <t>-10,53; 7,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26,39; 48,5</t>
+          <t>26,93; 48,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34,43; 97,93</t>
+          <t>77,87; 106,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,93; 17,42</t>
+          <t>0,19; 18,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,62; 48,68</t>
+          <t>28,56; 48,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,59; 93,87</t>
+          <t>77,28; 100,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,48</t>
+          <t>-2,07; 10,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30,89; 44,55</t>
+          <t>30,26; 44,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53,66; 91,33</t>
+          <t>80,87; 98,57</t>
         </is>
       </c>
     </row>
